--- a/CRM_NUVA_OXI.xlsx
+++ b/CRM_NUVA_OXI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimen\OneDrive\Escritorio\Proyecto-Nuva-Oxi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42250A4A-F654-4F40-99CA-56E6BFE63941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DA912A-6290-47D9-8F97-0816E7604A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="3300" windowWidth="8120" windowHeight="6000" firstSheet="12" activeTab="13" xr2:uid="{B976C6BC-3F23-46F3-B9AF-005A9C4F19E5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="12" activeTab="13" xr2:uid="{B976C6BC-3F23-46F3-B9AF-005A9C4F19E5}"/>
   </bookViews>
   <sheets>
     <sheet name="13_Dashboard" sheetId="14" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="411">
   <si>
     <t>PARAMETROS GLOBALES</t>
   </si>
@@ -1298,6 +1298,9 @@
   </si>
   <si>
     <t>Nota: Dashboard con formulas SUMIFS/COUNTIF. El analisis cruzado (sell-in vs sell-out, forecast) vive en CONSOLIDADO (8 reporteria).</t>
+  </si>
+  <si>
+    <t>Ultima actualizacion: 2026-07-06 15:50</t>
   </si>
 </sst>
 </file>
@@ -1413,54 +1416,10 @@
   </cellStyles>
   <dxfs count="29">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2C2C58"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF2C2C58"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -1516,10 +1475,32 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#.##0"/>
+      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#.##0"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2C2C58"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1576,12 +1557,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
@@ -1665,6 +1640,12 @@
       <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1691,6 +1672,12 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#.##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#.##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
@@ -1774,7 +1761,29 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF2C2C58"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1801,12 +1810,6 @@
       </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1821,7 +1824,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{1D7692FD-49E6-4210-9B12-6FE1196DEF3E}" name="tblPOP" displayName="tblPOP" ref="A2:E9" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{1D7692FD-49E6-4210-9B12-6FE1196DEF3E}" name="tblPOP" displayName="tblPOP" ref="A2:E9" totalsRowShown="0" headerRowDxfId="28">
   <autoFilter ref="A2:E9" xr:uid="{1D7692FD-49E6-4210-9B12-6FE1196DEF3E}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{EA305D2E-3A75-4F5C-81DB-D0CC46955A6B}" name="Codigo"/>
@@ -1835,11 +1838,11 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43E9119E-3188-41FF-B217-F8792392E995}" name="tblVisitas" displayName="tblVisitas" ref="A1:J4" totalsRowShown="0" headerRowDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{43E9119E-3188-41FF-B217-F8792392E995}" name="tblVisitas" displayName="tblVisitas" ref="A1:J4" totalsRowShown="0" headerRowDxfId="10">
   <autoFilter ref="A1:J4" xr:uid="{43E9119E-3188-41FF-B217-F8792392E995}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{120BBCD0-7031-476C-A6AB-2A8D379A1A55}" name="ID_Visita"/>
-    <tableColumn id="2" xr3:uid="{2A00455D-C9B7-42D0-83AC-5AFCAD98CDEF}" name="Fecha" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{2A00455D-C9B7-42D0-83AC-5AFCAD98CDEF}" name="Fecha" dataDxfId="9"/>
     <tableColumn id="3" xr3:uid="{9446481E-6671-4079-9D7A-22E07FD62E37}" name="Resp"/>
     <tableColumn id="4" xr3:uid="{1DEA332C-DEAA-42F1-8127-3A8BD4B71B52}" name="ID_Cliente"/>
     <tableColumn id="5" xr3:uid="{2150469E-29AD-4B42-939F-F9FD4F5C3477}" name="ID_PDV"/>
@@ -1847,14 +1850,14 @@
     <tableColumn id="7" xr3:uid="{36C946D5-B007-4B92-BB54-97C729C47071}" name="Objetivo"/>
     <tableColumn id="8" xr3:uid="{C51F5BAF-684A-43FD-B227-702276CB9D39}" name="Estado_Visita"/>
     <tableColumn id="9" xr3:uid="{3FA0A002-4BCE-4D9F-829A-E38B7C48BEEB}" name="Proxima_Accion"/>
-    <tableColumn id="10" xr3:uid="{2DA6BE20-7FE3-4F95-A430-43DB4C385F04}" name="Fecha_Proxima" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{2DA6BE20-7FE3-4F95-A430-43DB4C385F04}" name="Fecha_Proxima" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{26CA38AE-0657-4B1A-BD55-AC4FF41E206C}" name="tblPrioriz" displayName="tblPrioriz" ref="A1:J7" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{26CA38AE-0657-4B1A-BD55-AC4FF41E206C}" name="tblPrioriz" displayName="tblPrioriz" ref="A1:J7" totalsRowShown="0" headerRowDxfId="7">
   <autoFilter ref="A1:J7" xr:uid="{26CA38AE-0657-4B1A-BD55-AC4FF41E206C}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{9B76CD19-DB02-49C2-96D4-7D6AF43C5C23}" name="ID_PDV"/>
@@ -1877,7 +1880,7 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{881109BE-A7EB-4EF0-917F-E02ED0E815DC}" name="tblSKUs" displayName="tblSKUs" ref="A1:J7" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{881109BE-A7EB-4EF0-917F-E02ED0E815DC}" name="tblSKUs" displayName="tblSKUs" ref="A1:J7" totalsRowShown="0" headerRowDxfId="6">
   <autoFilter ref="A1:J7" xr:uid="{881109BE-A7EB-4EF0-917F-E02ED0E815DC}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{6BFFCECE-1890-4E95-AEC4-BDBFCDA64077}" name="SKU"/>
@@ -1889,7 +1892,7 @@
       <calculatedColumnFormula>E2/(1+IVA)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{EFA976AF-CFD0-4DAE-900C-FE2EDD0D636F}" name="Costo_Unit"/>
-    <tableColumn id="8" xr3:uid="{7F8A4117-D204-4A65-A186-187D81BEF039}" name="Vigente_Desde" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{7F8A4117-D204-4A65-A186-187D81BEF039}" name="Vigente_Desde" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{E0517566-FAF5-4866-B6FC-98DFE979861A}" name="Vigente_Hasta"/>
     <tableColumn id="10" xr3:uid="{5A6EAFB2-7FCB-4827-B8AA-F09E733E8BC4}" name="Activo"/>
   </tableColumns>
@@ -1898,7 +1901,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{61A4D1DC-88CD-4BED-B4B2-339797554A62}" name="tblPDV" displayName="tblPDV" ref="A1:M24" totalsRowShown="0" headerRowDxfId="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{61A4D1DC-88CD-4BED-B4B2-339797554A62}" name="tblPDV" displayName="tblPDV" ref="A1:M24" totalsRowShown="0" headerRowDxfId="4">
   <autoFilter ref="A1:M24" xr:uid="{61A4D1DC-88CD-4BED-B4B2-339797554A62}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{C08B551B-87CC-4720-BFAC-FA271E9976B7}" name="ID_PDV"/>
@@ -1910,7 +1913,7 @@
     <tableColumn id="7" xr3:uid="{CEDFB0CE-3EA5-45BE-A0B8-9A162DCEDCD0}" name="Estado"/>
     <tableColumn id="8" xr3:uid="{93636FD8-63CB-4F9A-8AA5-EB2CC33F6D29}" name="Formato_Recom"/>
     <tableColumn id="9" xr3:uid="{6910C63E-FBB6-4F0B-814B-0122AED2AF8C}" name="Frecuencia_Visita"/>
-    <tableColumn id="10" xr3:uid="{7266072B-CC86-4273-8FBB-A03C71690733}" name="Fecha_Entrada" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{7266072B-CC86-4273-8FBB-A03C71690733}" name="Fecha_Entrada" dataDxfId="3"/>
     <tableColumn id="11" xr3:uid="{85108DEC-B546-4506-8EB6-F79F615BE833}" name="Meta_Ago"/>
     <tableColumn id="12" xr3:uid="{E55660B3-755C-4107-91BC-BC2097BA8B0C}" name="Meta_Sep"/>
     <tableColumn id="13" xr3:uid="{6FF8F65F-8A6A-4BBF-AA0C-4CFBBB344641}" name="Meta_Oct"/>
@@ -1920,7 +1923,7 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EAE9785-210D-4CA7-AB32-DBE919E0F661}" name="tblClientes" displayName="tblClientes" ref="A1:O8" totalsRowShown="0" headerRowDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9EAE9785-210D-4CA7-AB32-DBE919E0F661}" name="tblClientes" displayName="tblClientes" ref="A1:O8" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:O8" xr:uid="{9EAE9785-210D-4CA7-AB32-DBE919E0F661}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{DDB6E6EE-0952-4FDA-97F1-3B1653FCD570}" name="ID_Cliente"/>
@@ -1933,9 +1936,9 @@
     <tableColumn id="8" xr3:uid="{00096243-B705-4924-BA83-76AD1621679C}" name="Contacto"/>
     <tableColumn id="9" xr3:uid="{46F3896D-A636-4BB4-BBBD-A6EB5FE893D3}" name="Resp"/>
     <tableColumn id="10" xr3:uid="{2B53EA97-1897-436B-B715-6B7BA91EF779}" name="Estado"/>
-    <tableColumn id="11" xr3:uid="{3D99CE76-4072-4C89-A8EF-D79F1A233218}" name="Fecha_Ult_Contacto" dataDxfId="28"/>
+    <tableColumn id="11" xr3:uid="{3D99CE76-4072-4C89-A8EF-D79F1A233218}" name="Fecha_Ult_Contacto" dataDxfId="1"/>
     <tableColumn id="12" xr3:uid="{43C5FF22-6BFD-4463-8FFA-B46A6AA7FC2F}" name="Proxima_Accion"/>
-    <tableColumn id="13" xr3:uid="{CBD59683-19D2-45C6-8835-EAFC90AA5C56}" name="Fecha_Proxima" dataDxfId="27"/>
+    <tableColumn id="13" xr3:uid="{CBD59683-19D2-45C6-8835-EAFC90AA5C56}" name="Fecha_Proxima" dataDxfId="0"/>
     <tableColumn id="14" xr3:uid="{4EED399A-D31F-45C3-B425-5DF17D79CB98}" name="Fuente"/>
     <tableColumn id="15" xr3:uid="{9F7433C6-C1A8-4574-9648-1AA4545F7FD4}" name="Notas"/>
   </tableColumns>
@@ -1944,7 +1947,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D7C0782F-70A1-4BEF-87AD-C04BC3DF03B3}" name="tblActivaciones" displayName="tblActivaciones" ref="A12:F18" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{D7C0782F-70A1-4BEF-87AD-C04BC3DF03B3}" name="tblActivaciones" displayName="tblActivaciones" ref="A12:F18" totalsRowShown="0" headerRowDxfId="27">
   <autoFilter ref="A12:F18" xr:uid="{D7C0782F-70A1-4BEF-87AD-C04BC3DF03B3}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{E2FA7297-9387-4B40-9828-96E971775EDF}" name="Fecha"/>
@@ -1959,10 +1962,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{71F04203-980F-4B67-BB36-4BB4AA8B90A4}" name="tblDecisiones" displayName="tblDecisiones" ref="A1:G7" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{71F04203-980F-4B67-BB36-4BB4AA8B90A4}" name="tblDecisiones" displayName="tblDecisiones" ref="A1:G7" totalsRowShown="0" headerRowDxfId="26">
   <autoFilter ref="A1:G7" xr:uid="{71F04203-980F-4B67-BB36-4BB4AA8B90A4}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{5C830DC2-1F09-414F-BDEC-2682A611D101}" name="Fecha" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{5C830DC2-1F09-414F-BDEC-2682A611D101}" name="Fecha" dataDxfId="25"/>
     <tableColumn id="2" xr3:uid="{37517EFC-A768-4CD4-AAB3-5E694CE40DDA}" name="Tema"/>
     <tableColumn id="3" xr3:uid="{31E30816-92DA-4985-823B-C1F9926322A8}" name="Decision"/>
     <tableColumn id="4" xr3:uid="{B9712806-DB7C-426A-9EFA-3093176FD034}" name="Responsable"/>
@@ -1975,7 +1978,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{017D7869-115E-47A1-AD46-B4FE57391F4F}" name="tblCondiciones" displayName="tblCondiciones" ref="A1:J4" totalsRowShown="0" headerRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{017D7869-115E-47A1-AD46-B4FE57391F4F}" name="tblCondiciones" displayName="tblCondiciones" ref="A1:J4" totalsRowShown="0" headerRowDxfId="24">
   <autoFilter ref="A1:J4" xr:uid="{017D7869-115E-47A1-AD46-B4FE57391F4F}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{A6E931A2-548E-487B-8FB0-A480BA4F0C47}" name="Canal"/>
@@ -2000,20 +2003,20 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F342F577-D356-4BA7-A923-A06C5B81243E}" name="tblSellIn" displayName="tblSellIn" ref="A1:S7" totalsRowShown="0" headerRowDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{F342F577-D356-4BA7-A923-A06C5B81243E}" name="tblSellIn" displayName="tblSellIn" ref="A1:S7" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="A1:S7" xr:uid="{F342F577-D356-4BA7-A923-A06C5B81243E}"/>
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{390C4B17-4579-497D-9AF6-8BC0441AA357}" name="ID_Venta"/>
-    <tableColumn id="2" xr3:uid="{055B2713-FB72-4683-86AE-2846D4AD2868}" name="Fecha" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{055B2713-FB72-4683-86AE-2846D4AD2868}" name="Fecha" dataDxfId="22"/>
     <tableColumn id="3" xr3:uid="{AD0C802F-F872-44C9-B3BD-81BFE5C4CFC5}" name="ID_Cliente"/>
     <tableColumn id="4" xr3:uid="{F07D2F31-2D50-4000-BEB1-F23E12679DD2}" name="ID_PDV"/>
     <tableColumn id="5" xr3:uid="{9994CD14-8A0E-4DA1-BC1B-67580B2BC772}" name="SKU"/>
     <tableColumn id="6" xr3:uid="{61BB444D-1FFF-4976-AA55-D960219A7966}" name="N_OC"/>
     <tableColumn id="7" xr3:uid="{BA810158-8927-461C-9F5E-7E06E99632A4}" name="N_Factura"/>
     <tableColumn id="8" xr3:uid="{5F3B6CC9-B7C4-4375-9200-2B35D9F9526B}" name="Uds"/>
-    <tableColumn id="9" xr3:uid="{419A249A-681C-4BFD-93EA-342A6E4CCD32}" name="Precio_Unit_Neto" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{419A249A-681C-4BFD-93EA-342A6E4CCD32}" name="Precio_Unit_Neto" dataDxfId="21"/>
     <tableColumn id="10" xr3:uid="{F70CEB0A-4C10-4901-AD0C-497781A3351F}" name="%Desc"/>
-    <tableColumn id="11" xr3:uid="{55B6F02B-E8CC-4820-8F1F-3616C61D8219}" name="Venta_Neta" dataDxfId="5">
+    <tableColumn id="11" xr3:uid="{55B6F02B-E8CC-4820-8F1F-3616C61D8219}" name="Venta_Neta" dataDxfId="20">
       <calculatedColumnFormula>ROUND(H2*I2*(1-J2),0)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="12" xr3:uid="{E42622DD-3261-4A92-A630-97AD2C7DD702}" name="Costo_Total"/>
@@ -2022,7 +2025,7 @@
     </tableColumn>
     <tableColumn id="14" xr3:uid="{F9C80FEE-C724-44FD-85AE-0574B70060ED}" name="Estado_Factura"/>
     <tableColumn id="15" xr3:uid="{61194893-A5F1-4F98-AF3A-2E44D021EC34}" name="Plazo_Dias"/>
-    <tableColumn id="16" xr3:uid="{C14B49ED-2FE3-47E7-ABBD-A39F1A639901}" name="Fecha_Venc" dataDxfId="8">
+    <tableColumn id="16" xr3:uid="{C14B49ED-2FE3-47E7-ABBD-A39F1A639901}" name="Fecha_Venc" dataDxfId="19">
       <calculatedColumnFormula>B2+O2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="17" xr3:uid="{1F69FF28-66C3-467F-BB66-90F1155CDFB2}" name="Fecha_Pago"/>
@@ -2034,17 +2037,17 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AC63771F-A628-4BAA-B5EC-A2B76CC9153D}" name="tblPedidos" displayName="tblPedidos" ref="A1:M4" totalsRowShown="0" headerRowDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{AC63771F-A628-4BAA-B5EC-A2B76CC9153D}" name="tblPedidos" displayName="tblPedidos" ref="A1:M4" totalsRowShown="0" headerRowDxfId="18">
   <autoFilter ref="A1:M4" xr:uid="{AC63771F-A628-4BAA-B5EC-A2B76CC9153D}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{D6C55F6A-AB15-4241-BE2E-69EA0F2007C3}" name="ID_Pedido"/>
     <tableColumn id="2" xr3:uid="{D4992380-BD45-43D4-932F-99FF43BFA75B}" name="ID_Cliente"/>
-    <tableColumn id="3" xr3:uid="{BDC99F6A-4404-4396-8AED-0896E95A9896}" name="Fecha_OC" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{BDC99F6A-4404-4396-8AED-0896E95A9896}" name="Fecha_OC" dataDxfId="17"/>
     <tableColumn id="4" xr3:uid="{49799C09-05DB-43EA-9DA8-7FB92996A135}" name="N_OC"/>
     <tableColumn id="5" xr3:uid="{A3545527-8A35-407D-A235-AC000E0869E7}" name="Monto_OC"/>
-    <tableColumn id="6" xr3:uid="{3DED93DA-E4CA-4033-94FE-7EDF7DBAF791}" name="Fecha_Despacho" dataDxfId="12"/>
+    <tableColumn id="6" xr3:uid="{3DED93DA-E4CA-4033-94FE-7EDF7DBAF791}" name="Fecha_Despacho" dataDxfId="16"/>
     <tableColumn id="7" xr3:uid="{0DABEECF-BF6C-4638-A9E5-23BA6A1496F0}" name="N_Guia"/>
-    <tableColumn id="8" xr3:uid="{10575548-9D4C-4930-A009-A1B3F9E02D36}" name="Fecha_Factura" dataDxfId="11"/>
+    <tableColumn id="8" xr3:uid="{10575548-9D4C-4930-A009-A1B3F9E02D36}" name="Fecha_Factura" dataDxfId="15"/>
     <tableColumn id="9" xr3:uid="{3DDF4E46-E3E8-481E-9B9D-F2753894813C}" name="N_Factura"/>
     <tableColumn id="10" xr3:uid="{F81ABBB4-4DE2-4CA6-9B41-16D0345BA669}" name="Estado"/>
     <tableColumn id="11" xr3:uid="{56081CCC-6B64-4B64-8C0A-60FE2425B91F}" name="Fecha_Pago_Real"/>
@@ -2058,7 +2061,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{8821A362-FFF0-4C90-8B37-CDB881810372}" name="tblStock" displayName="tblStock" ref="A2:I8" totalsRowShown="0" headerRowDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{8821A362-FFF0-4C90-8B37-CDB881810372}" name="tblStock" displayName="tblStock" ref="A2:I8" totalsRowShown="0" headerRowDxfId="14">
   <autoFilter ref="A2:I8" xr:uid="{8821A362-FFF0-4C90-8B37-CDB881810372}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{DB194AF3-12D9-43DA-91A6-0415B02AB7B3}" name="SKU"/>
@@ -2080,7 +2083,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{01F53D63-5D64-4895-AFAD-2AFCBFCB32A3}" name="tblInventarioPDV" displayName="tblInventarioPDV" ref="A11:H14" totalsRowShown="0" headerRowDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{01F53D63-5D64-4895-AFAD-2AFCBFCB32A3}" name="tblInventarioPDV" displayName="tblInventarioPDV" ref="A11:H14" totalsRowShown="0" headerRowDxfId="13">
   <autoFilter ref="A11:H14" xr:uid="{01F53D63-5D64-4895-AFAD-2AFCBFCB32A3}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{4726D094-B51E-45ED-8526-5081AC901D3F}" name="ID_PDV"/>
@@ -2103,10 +2106,10 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7BB589DC-5099-4177-BFF7-B97D742105BE}" name="tblRegistroPDV" displayName="tblRegistroPDV" ref="A1:Q3" totalsRowShown="0" headerRowDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{7BB589DC-5099-4177-BFF7-B97D742105BE}" name="tblRegistroPDV" displayName="tblRegistroPDV" ref="A1:Q3" totalsRowShown="0" headerRowDxfId="12">
   <autoFilter ref="A1:Q3" xr:uid="{7BB589DC-5099-4177-BFF7-B97D742105BE}"/>
   <tableColumns count="17">
-    <tableColumn id="1" xr3:uid="{E6B19030-5E27-42E4-B38C-3AE902CE7629}" name="Fecha" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{E6B19030-5E27-42E4-B38C-3AE902CE7629}" name="Fecha" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{3177DAE2-582D-4B00-ABCF-15A29F62BD63}" name="ID_PDV"/>
     <tableColumn id="3" xr3:uid="{48601E5D-0623-4024-B6FA-53B295B190BC}" name="Resp"/>
     <tableColumn id="4" xr3:uid="{805A8688-60A6-4513-B494-0755D844A3A1}" name="Formato_Presente"/>
@@ -2447,7 +2450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B9985BF-8852-4521-89C1-FBA1FC939D96}">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="110.81640625" bestFit="1" customWidth="1"/>
@@ -2596,6 +2599,11 @@
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>409</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -2678,11 +2686,11 @@
         <v>4</v>
       </c>
       <c r="I2">
-        <f>SUM(B2)+G2+H2+F2</f>
+        <f t="shared" ref="I2:I7" si="0">SUM(B2)+G2+H2+F2</f>
         <v>10</v>
       </c>
       <c r="J2" t="str">
-        <f>IF(I2&gt;=18,"Alta",IF(I2&gt;=12,"Media","Baja"))</f>
+        <f t="shared" ref="J2:J7" si="1">IF(I2&gt;=18,"Alta",IF(I2&gt;=12,"Media","Baja"))</f>
         <v>Baja</v>
       </c>
     </row>
@@ -2712,11 +2720,11 @@
         <v>5</v>
       </c>
       <c r="I3">
-        <f>SUM(B3)+G3+H3+F3</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="J3" t="str">
-        <f>IF(I3&gt;=18,"Alta",IF(I3&gt;=12,"Media","Baja"))</f>
+        <f t="shared" si="1"/>
         <v>Media</v>
       </c>
     </row>
@@ -2746,11 +2754,11 @@
         <v>4</v>
       </c>
       <c r="I4">
-        <f>SUM(B4)+G4+H4+F4</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="J4" t="str">
-        <f>IF(I4&gt;=18,"Alta",IF(I4&gt;=12,"Media","Baja"))</f>
+        <f t="shared" si="1"/>
         <v>Media</v>
       </c>
     </row>
@@ -2780,11 +2788,11 @@
         <v>4</v>
       </c>
       <c r="I5">
-        <f>SUM(B5)+G5+H5+F5</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="J5" t="str">
-        <f>IF(I5&gt;=18,"Alta",IF(I5&gt;=12,"Media","Baja"))</f>
+        <f t="shared" si="1"/>
         <v>Baja</v>
       </c>
     </row>
@@ -2814,11 +2822,11 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <f>SUM(B6)+G6+H6+F6</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="J6" t="str">
-        <f>IF(I6&gt;=18,"Alta",IF(I6&gt;=12,"Media","Baja"))</f>
+        <f t="shared" si="1"/>
         <v>Baja</v>
       </c>
     </row>
@@ -2848,11 +2856,11 @@
         <v>4</v>
       </c>
       <c r="I7">
-        <f>SUM(B7)+G7+H7+F7</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="J7" t="str">
-        <f>IF(I7&gt;=18,"Alta",IF(I7&gt;=12,"Media","Baja"))</f>
+        <f t="shared" si="1"/>
         <v>Baja</v>
       </c>
     </row>
@@ -2930,7 +2938,7 @@
         <v>1900</v>
       </c>
       <c r="F2">
-        <f>E2/(1+IVA)</f>
+        <f t="shared" ref="F2:F7" si="0">E2/(1+IVA)</f>
         <v>1596.6386554621849</v>
       </c>
       <c r="G2">
@@ -2960,7 +2968,7 @@
         <v>1900</v>
       </c>
       <c r="F3">
-        <f>E3/(1+IVA)</f>
+        <f t="shared" si="0"/>
         <v>1596.6386554621849</v>
       </c>
       <c r="G3">
@@ -2990,7 +2998,7 @@
         <v>1900</v>
       </c>
       <c r="F4">
-        <f>E4/(1+IVA)</f>
+        <f t="shared" si="0"/>
         <v>1596.6386554621849</v>
       </c>
       <c r="G4">
@@ -3020,7 +3028,7 @@
         <v>5900</v>
       </c>
       <c r="F5">
-        <f>E5/(1+IVA)</f>
+        <f t="shared" si="0"/>
         <v>4957.9831932773113</v>
       </c>
       <c r="G5">
@@ -3050,7 +3058,7 @@
         <v>5900</v>
       </c>
       <c r="F6">
-        <f>E6/(1+IVA)</f>
+        <f t="shared" si="0"/>
         <v>4957.9831932773113</v>
       </c>
       <c r="G6">
@@ -3080,7 +3088,7 @@
         <v>5900</v>
       </c>
       <c r="F7">
-        <f>E7/(1+IVA)</f>
+        <f t="shared" si="0"/>
         <v>4957.9831932773113</v>
       </c>
       <c r="G7">
@@ -5565,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="K2" s="8">
-        <f>ROUND(H2*I2*(1-J2),0)</f>
+        <f t="shared" ref="K2:K7" si="0">ROUND(H2*I2*(1-J2),0)</f>
         <v>19160</v>
       </c>
       <c r="L2">
@@ -5573,7 +5581,7 @@
         <v>3000</v>
       </c>
       <c r="M2">
-        <f>K2-L2</f>
+        <f t="shared" ref="M2:M7" si="1">K2-L2</f>
         <v>16160</v>
       </c>
       <c r="N2" t="s">
@@ -5583,7 +5591,7 @@
         <v>30</v>
       </c>
       <c r="P2" s="6">
-        <f>B2+O2</f>
+        <f t="shared" ref="P2:P7" si="2">B2+O2</f>
         <v>46057</v>
       </c>
       <c r="Q2" s="6">
@@ -5625,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="K3" s="8">
-        <f>ROUND(H3*I3*(1-J3),0)</f>
+        <f t="shared" si="0"/>
         <v>12773</v>
       </c>
       <c r="L3">
@@ -5633,7 +5641,7 @@
         <v>2000</v>
       </c>
       <c r="M3">
-        <f>K3-L3</f>
+        <f t="shared" si="1"/>
         <v>10773</v>
       </c>
       <c r="N3" t="s">
@@ -5643,7 +5651,7 @@
         <v>30</v>
       </c>
       <c r="P3" s="6">
-        <f>B3+O3</f>
+        <f t="shared" si="2"/>
         <v>46058</v>
       </c>
       <c r="Q3" s="6">
@@ -5685,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="8">
-        <f>ROUND(H4*I4*(1-J4),0)</f>
+        <f t="shared" si="0"/>
         <v>14370</v>
       </c>
       <c r="L4">
@@ -5693,7 +5701,7 @@
         <v>2250</v>
       </c>
       <c r="M4">
-        <f>K4-L4</f>
+        <f t="shared" si="1"/>
         <v>12120</v>
       </c>
       <c r="N4" t="s">
@@ -5703,7 +5711,7 @@
         <v>30</v>
       </c>
       <c r="P4" s="6">
-        <f>B4+O4</f>
+        <f t="shared" si="2"/>
         <v>46059</v>
       </c>
       <c r="R4" t="s">
@@ -5742,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="K5" s="8">
-        <f>ROUND(H5*I5*(1-J5),0)</f>
+        <f t="shared" si="0"/>
         <v>24790</v>
       </c>
       <c r="L5">
@@ -5750,7 +5758,7 @@
         <v>5000</v>
       </c>
       <c r="M5">
-        <f>K5-L5</f>
+        <f t="shared" si="1"/>
         <v>19790</v>
       </c>
       <c r="N5" t="s">
@@ -5760,7 +5768,7 @@
         <v>30</v>
       </c>
       <c r="P5" s="6">
-        <f>B5+O5</f>
+        <f t="shared" si="2"/>
         <v>46061</v>
       </c>
       <c r="Q5" s="6">
@@ -5802,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="8">
-        <f>ROUND(H6*I6*(1-J6),0)</f>
+        <f t="shared" si="0"/>
         <v>39664</v>
       </c>
       <c r="L6">
@@ -5810,7 +5818,7 @@
         <v>8000</v>
       </c>
       <c r="M6">
-        <f>K6-L6</f>
+        <f t="shared" si="1"/>
         <v>31664</v>
       </c>
       <c r="N6" t="s">
@@ -5820,7 +5828,7 @@
         <v>30</v>
       </c>
       <c r="P6" s="6">
-        <f>B6+O6</f>
+        <f t="shared" si="2"/>
         <v>46064</v>
       </c>
       <c r="R6" t="s">
@@ -5862,7 +5870,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="8">
-        <f>ROUND(H7*I7*(1-J7),0)</f>
+        <f t="shared" si="0"/>
         <v>247899</v>
       </c>
       <c r="L7">
@@ -5870,7 +5878,7 @@
         <v>50000</v>
       </c>
       <c r="M7">
-        <f>K7-L7</f>
+        <f t="shared" si="1"/>
         <v>197899</v>
       </c>
       <c r="N7" t="s">
@@ -5880,7 +5888,7 @@
         <v>30</v>
       </c>
       <c r="P7" s="6">
-        <f>B7+O7</f>
+        <f t="shared" si="2"/>
         <v>46065</v>
       </c>
       <c r="R7" t="s">
@@ -6190,14 +6198,14 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <f>B3-C3-D3-E3-F3</f>
+        <f t="shared" ref="G3:G8" si="0">B3-C3-D3-E3-F3</f>
         <v>0</v>
       </c>
       <c r="H3">
         <v>30</v>
       </c>
       <c r="I3" t="str">
-        <f>IF(G3&lt;=0,"QUIEBRE",IF(G3&lt;=H3,"BAJO","OK"))</f>
+        <f t="shared" ref="I3:I8" si="1">IF(G3&lt;=0,"QUIEBRE",IF(G3&lt;=H3,"BAJO","OK"))</f>
         <v>QUIEBRE</v>
       </c>
     </row>
@@ -6221,14 +6229,14 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <f>B4-C4-D4-E4-F4</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H4">
         <v>30</v>
       </c>
       <c r="I4" t="str">
-        <f>IF(G4&lt;=0,"QUIEBRE",IF(G4&lt;=H4,"BAJO","OK"))</f>
+        <f t="shared" si="1"/>
         <v>QUIEBRE</v>
       </c>
     </row>
@@ -6252,14 +6260,14 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <f>B5-C5-D5-E5-F5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H5">
         <v>30</v>
       </c>
       <c r="I5" t="str">
-        <f>IF(G5&lt;=0,"QUIEBRE",IF(G5&lt;=H5,"BAJO","OK"))</f>
+        <f t="shared" si="1"/>
         <v>QUIEBRE</v>
       </c>
     </row>
@@ -6283,14 +6291,14 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <f>B6-C6-D6-E6-F6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6">
         <v>30</v>
       </c>
       <c r="I6" t="str">
-        <f>IF(G6&lt;=0,"QUIEBRE",IF(G6&lt;=H6,"BAJO","OK"))</f>
+        <f t="shared" si="1"/>
         <v>QUIEBRE</v>
       </c>
     </row>
@@ -6314,14 +6322,14 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <f>B7-C7-D7-E7-F7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H7">
         <v>30</v>
       </c>
       <c r="I7" t="str">
-        <f>IF(G7&lt;=0,"QUIEBRE",IF(G7&lt;=H7,"BAJO","OK"))</f>
+        <f t="shared" si="1"/>
         <v>QUIEBRE</v>
       </c>
     </row>
@@ -6345,14 +6353,14 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <f>B8-C8-D8-E8-F8</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H8">
         <v>30</v>
       </c>
       <c r="I8" t="str">
-        <f>IF(G8&lt;=0,"QUIEBRE",IF(G8&lt;=H8,"BAJO","OK"))</f>
+        <f t="shared" si="1"/>
         <v>QUIEBRE</v>
       </c>
     </row>

--- a/CRM_NUVA_OXI.xlsx
+++ b/CRM_NUVA_OXI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jimen\OneDrive\Escritorio\Proyecto-Nuva-Oxi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DA912A-6290-47D9-8F97-0816E7604A27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5079DB7-0119-4F5C-97C2-A25B0733689F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="12" activeTab="13" xr2:uid="{B976C6BC-3F23-46F3-B9AF-005A9C4F19E5}"/>
   </bookViews>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="412">
   <si>
     <t>PARAMETROS GLOBALES</t>
   </si>
@@ -670,9 +670,6 @@
     <t>SKU-CAC-U</t>
   </si>
   <si>
-    <t>Barra Cacao 40g</t>
-  </si>
-  <si>
     <t>Cacao</t>
   </si>
   <si>
@@ -682,39 +679,24 @@
     <t>SKU-MAN-U</t>
   </si>
   <si>
-    <t>Barra Mani 40g</t>
-  </si>
-  <si>
     <t>Mani</t>
   </si>
   <si>
     <t>SKU-FRU-U</t>
   </si>
   <si>
-    <t>Barra Frutal 40g</t>
-  </si>
-  <si>
     <t>Frutal</t>
   </si>
   <si>
     <t>SKU-CAC-4</t>
   </si>
   <si>
-    <t>Estuche Cacao x4</t>
-  </si>
-  <si>
     <t>SKU-MAN-4</t>
   </si>
   <si>
-    <t>Estuche Mani x4</t>
-  </si>
-  <si>
     <t>SKU-FRU-4</t>
   </si>
   <si>
-    <t>Estuche Frutal x4</t>
-  </si>
-  <si>
     <t>Nota: habra 3er precio futuro (estuche ~6490) y descuentos 20-30%. Versionar con Vigente_Desde/Hasta.</t>
   </si>
   <si>
@@ -1081,9 +1063,6 @@
     <t>Comentario</t>
   </si>
   <si>
-    <t>Modelo BCT/VCT</t>
-  </si>
-  <si>
     <t>Definir si opera full, parcial o solo apoyo</t>
   </si>
   <si>
@@ -1301,6 +1280,30 @@
   </si>
   <si>
     <t>Ultima actualizacion: 2026-07-06 15:50</t>
+  </si>
+  <si>
+    <t>Barra Cacao 35g</t>
+  </si>
+  <si>
+    <t>Barra Mani 35g</t>
+  </si>
+  <si>
+    <t>Barra Frutal 35g</t>
+  </si>
+  <si>
+    <t>Estuche Cacao 4x35g</t>
+  </si>
+  <si>
+    <t>Estuche Mani 4x35g</t>
+  </si>
+  <si>
+    <t>Estuche Frutal 4x35g</t>
+  </si>
+  <si>
+    <t>Precio premium (clientes que pagan mas): unitaria 2190 / estuche 6490. Aplicar por cliente/canal.</t>
+  </si>
+  <si>
+    <t>Modelo integracion VCT</t>
   </si>
 </sst>
 </file>
@@ -2460,12 +2463,12 @@
   <sheetData>
     <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.5">
       <c r="A1" s="10" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -2473,7 +2476,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="B4" s="8">
         <f>SUM('09_Sell_In'!H2:H7)</f>
@@ -2482,7 +2485,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="B5" s="8">
         <f>SUM('09_Sell_In'!K2:K7)</f>
@@ -2491,7 +2494,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="B6" s="8">
         <f>SUM('09_Sell_In'!M2:M7)</f>
@@ -2500,7 +2503,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B7" s="8">
         <f>COUNTIF('02_Maestro_PDV'!G:G,"Activo")</f>
@@ -2509,7 +2512,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B8" s="8">
         <f>COUNTA('02_Maestro_PDV'!A2:A100)</f>
@@ -2518,7 +2521,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="B9" s="8">
         <f>COUNTA('05_Plan_Visitas'!A2:A500)</f>
@@ -2527,7 +2530,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B10" s="8">
         <f>COUNTIF('11_Tareas_Decisiones'!E:E,"Abierta")</f>
@@ -2536,74 +2539,74 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>399</v>
+        <v>392</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B15" s="8">
         <f ca="1">SUMIFS('09_Sell_In'!K2:K7,'09_Sell_In'!N2:N7,"Emitida",'09_Sell_In'!P2:P7,"&gt;"&amp;(TODAY()-15))</f>
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B16" s="8">
         <f>SUMIFS('09_Sell_In'!K2:K7,'09_Sell_In'!N2:N7,"Emitida")*0</f>
         <v>0</v>
       </c>
       <c r="C16" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B17" s="8">
         <v>0</v>
       </c>
       <c r="C17" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="B18" s="8">
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>
@@ -2633,31 +2636,31 @@
         <v>124</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2874,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF84F5E6-D8C4-4C4F-B9D2-B561F2294804}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
@@ -2925,21 +2928,21 @@
       <c r="A2" t="s">
         <v>199</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C2" t="s">
         <v>200</v>
-      </c>
-      <c r="C2" t="s">
-        <v>201</v>
       </c>
       <c r="D2" t="s">
         <v>21</v>
       </c>
       <c r="E2">
-        <v>1900</v>
+        <v>1990</v>
       </c>
       <c r="F2">
         <f t="shared" ref="F2:F7" si="0">E2/(1+IVA)</f>
-        <v>1596.6386554621849</v>
+        <v>1672.2689075630253</v>
       </c>
       <c r="G2">
         <v>250</v>
@@ -2948,28 +2951,28 @@
         <v>46023</v>
       </c>
       <c r="J2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C3" t="s">
         <v>203</v>
-      </c>
-      <c r="B3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C3" t="s">
-        <v>205</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
       </c>
       <c r="E3">
-        <v>1900</v>
+        <v>1990</v>
       </c>
       <c r="F3">
         <f t="shared" si="0"/>
-        <v>1596.6386554621849</v>
+        <v>1672.2689075630253</v>
       </c>
       <c r="G3">
         <v>250</v>
@@ -2978,28 +2981,28 @@
         <v>46023</v>
       </c>
       <c r="J3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>206</v>
-      </c>
-      <c r="B4" t="s">
-        <v>207</v>
+        <v>204</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>406</v>
       </c>
       <c r="C4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
       </c>
       <c r="E4">
-        <v>1900</v>
+        <v>1990</v>
       </c>
       <c r="F4">
         <f t="shared" si="0"/>
-        <v>1596.6386554621849</v>
+        <v>1672.2689075630253</v>
       </c>
       <c r="G4">
         <v>250</v>
@@ -3008,28 +3011,28 @@
         <v>46023</v>
       </c>
       <c r="J4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B5" t="s">
-        <v>210</v>
+        <v>206</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>407</v>
       </c>
       <c r="C5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
       </c>
       <c r="E5">
-        <v>5900</v>
+        <v>5990</v>
       </c>
       <c r="F5">
         <f t="shared" si="0"/>
-        <v>4957.9831932773113</v>
+        <v>5033.6134453781515</v>
       </c>
       <c r="G5">
         <v>1000</v>
@@ -3038,28 +3041,28 @@
         <v>46023</v>
       </c>
       <c r="J5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>211</v>
-      </c>
-      <c r="B6" t="s">
-        <v>212</v>
+        <v>207</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>408</v>
       </c>
       <c r="C6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
       </c>
       <c r="E6">
-        <v>5900</v>
+        <v>5990</v>
       </c>
       <c r="F6">
         <f t="shared" si="0"/>
-        <v>4957.9831932773113</v>
+        <v>5033.6134453781515</v>
       </c>
       <c r="G6">
         <v>1000</v>
@@ -3068,28 +3071,28 @@
         <v>46023</v>
       </c>
       <c r="J6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B7" t="s">
-        <v>214</v>
+        <v>208</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>409</v>
       </c>
       <c r="C7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D7" t="s">
         <v>22</v>
       </c>
       <c r="E7">
-        <v>5900</v>
+        <v>5990</v>
       </c>
       <c r="F7">
         <f t="shared" si="0"/>
-        <v>4957.9831932773113</v>
+        <v>5033.6134453781515</v>
       </c>
       <c r="G7">
         <v>1000</v>
@@ -3098,12 +3101,17 @@
         <v>46023</v>
       </c>
       <c r="J7" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>215</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
   </sheetData>
@@ -4856,168 +4864,168 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>192</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="B3" t="s">
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="D3">
         <v>85000</v>
       </c>
       <c r="E3" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B4" t="s">
         <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="D4">
         <v>8500</v>
       </c>
       <c r="E4" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="B5" t="s">
         <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>371</v>
+        <v>364</v>
       </c>
       <c r="D5">
         <v>4500</v>
       </c>
       <c r="E5" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="B6" t="s">
         <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="D6">
         <v>1200</v>
       </c>
       <c r="E6" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="B7" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
       <c r="C7" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="D7">
         <v>35000</v>
       </c>
       <c r="E7" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="B8" t="s">
         <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="D8">
         <v>25000</v>
       </c>
       <c r="E8" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="B9" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="C9" t="s">
-        <v>383</v>
+        <v>376</v>
       </c>
       <c r="D9">
         <v>12000</v>
       </c>
       <c r="E9" t="s">
-        <v>384</v>
+        <v>377</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
-        <v>385</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>124</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>80</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>387</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -5129,25 +5137,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -5155,22 +5163,22 @@
         <v>46209</v>
       </c>
       <c r="B2" t="s">
-        <v>337</v>
+        <v>411</v>
       </c>
       <c r="C2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F2" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="G2" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -5178,22 +5186,22 @@
         <v>46209</v>
       </c>
       <c r="B3" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="G3" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -5201,19 +5209,19 @@
         <v>46209</v>
       </c>
       <c r="B4" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C4" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D4" t="s">
         <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F4" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -5221,19 +5229,19 @@
         <v>46209</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="C5" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D5" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="E5" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="G5" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
@@ -5241,22 +5249,22 @@
         <v>46209</v>
       </c>
       <c r="B6" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C6" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F6" t="s">
         <v>88</v>
       </c>
       <c r="G6" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -5264,19 +5272,19 @@
         <v>46209</v>
       </c>
       <c r="B7" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="C7" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="G7" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
     </row>
   </sheetData>
@@ -5311,34 +5319,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>194</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>325</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -5487,10 +5495,10 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>73</v>
@@ -5502,40 +5510,40 @@
         <v>191</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H1" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="N1" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="O1" s="5" t="s">
         <v>309</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="Q1" s="5" t="s">
         <v>311</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>312</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>317</v>
       </c>
       <c r="R1" s="5" t="s">
         <v>80</v>
@@ -5561,7 +5569,7 @@
         <v>199</v>
       </c>
       <c r="G2" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="H2">
         <v>12</v>
@@ -5601,7 +5609,7 @@
         <v>10</v>
       </c>
       <c r="S2" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
@@ -5618,10 +5626,10 @@
         <v>176</v>
       </c>
       <c r="E3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G3" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="H3">
         <v>8</v>
@@ -5661,7 +5669,7 @@
         <v>10</v>
       </c>
       <c r="S3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
@@ -5678,10 +5686,10 @@
         <v>178</v>
       </c>
       <c r="E4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G4" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="H4">
         <v>9</v>
@@ -5718,7 +5726,7 @@
         <v>9</v>
       </c>
       <c r="S4" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
@@ -5735,10 +5743,10 @@
         <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G5" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -5778,7 +5786,7 @@
         <v>9</v>
       </c>
       <c r="S5" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
@@ -5795,10 +5803,10 @@
         <v>189</v>
       </c>
       <c r="E6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -5835,7 +5843,7 @@
         <v>9</v>
       </c>
       <c r="S6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
@@ -5852,13 +5860,13 @@
         <v>134</v>
       </c>
       <c r="E7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F7" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G7" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="H7">
         <v>50</v>
@@ -5895,12 +5903,12 @@
         <v>9</v>
       </c>
       <c r="S7" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="G8" s="1" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="H8" s="1">
         <f>SUM(H2:H7)</f>
@@ -5956,40 +5964,40 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>73</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>284</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>285</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>291</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>81</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>86</v>
@@ -5997,7 +6005,7 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B2" t="s">
         <v>87</v>
@@ -6006,7 +6014,7 @@
         <v>46032</v>
       </c>
       <c r="D2" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="E2">
         <v>295000</v>
@@ -6015,28 +6023,28 @@
         <v>46034</v>
       </c>
       <c r="G2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="H2" s="6">
         <v>46035</v>
       </c>
       <c r="I2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="J2" t="s">
         <v>47</v>
       </c>
       <c r="L2">
         <f ca="1">IF(K2="",TODAY()-C2,K2-C2)</f>
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M2" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="B3" t="s">
         <v>118</v>
@@ -6045,7 +6053,7 @@
         <v>46033</v>
       </c>
       <c r="D3" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="E3">
         <v>47200</v>
@@ -6054,13 +6062,13 @@
         <v>46034</v>
       </c>
       <c r="G3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="H3" s="6">
         <v>46034</v>
       </c>
       <c r="I3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="J3" t="s">
         <v>48</v>
@@ -6078,7 +6086,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B4" t="s">
         <v>94</v>
@@ -6087,7 +6095,7 @@
         <v>46027</v>
       </c>
       <c r="D4" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="E4">
         <v>22800</v>
@@ -6096,13 +6104,13 @@
         <v>46027</v>
       </c>
       <c r="G4" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="H4" s="6">
         <v>46027</v>
       </c>
       <c r="I4" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="J4" t="s">
         <v>49</v>
@@ -6146,7 +6154,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
@@ -6154,28 +6162,28 @@
         <v>191</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="I2" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
@@ -6211,7 +6219,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B4">
         <v>200</v>
@@ -6242,7 +6250,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B5">
         <v>200</v>
@@ -6273,7 +6281,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B6">
         <v>200</v>
@@ -6304,7 +6312,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B7">
         <v>200</v>
@@ -6335,7 +6343,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="B8">
         <v>200</v>
@@ -6366,7 +6374,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
@@ -6377,22 +6385,22 @@
         <v>191</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
@@ -6400,7 +6408,7 @@
         <v>134</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C12">
         <v>50</v>
@@ -6458,7 +6466,7 @@
         <v>189</v>
       </c>
       <c r="B14" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -6517,7 +6525,7 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>124</v>
@@ -6526,43 +6534,43 @@
         <v>80</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>249</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>255</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>83</v>
@@ -6595,28 +6603,28 @@
         <v>1900</v>
       </c>
       <c r="I2" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="J2" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="K2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L2" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="M2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="N2">
         <v>8</v>
       </c>
       <c r="O2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="Q2" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
@@ -6646,28 +6654,28 @@
         <v>5900</v>
       </c>
       <c r="I3" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="J3" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="K3" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="L3" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="M3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="Q3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -6705,10 +6713,10 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>80</v>
@@ -6720,13 +6728,13 @@
         <v>124</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="I1" s="5" t="s">
         <v>83</v>
@@ -6737,7 +6745,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B2" s="6">
         <v>46210</v>
@@ -6752,16 +6760,16 @@
         <v>174</v>
       </c>
       <c r="F2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G2" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="H2" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="I2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="J2" s="6">
         <v>46224</v>
@@ -6769,7 +6777,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B3" s="6">
         <v>46211</v>
@@ -6787,13 +6795,13 @@
         <v>122</v>
       </c>
       <c r="G3" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="H3" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="I3" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="J3" s="6">
         <v>46242</v>
@@ -6801,7 +6809,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B4" s="6">
         <v>46212</v>
@@ -6816,16 +6824,16 @@
         <v>134</v>
       </c>
       <c r="F4" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="G4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="H4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="I4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="J4" s="6">
         <v>46219</v>
